--- a/research/traditional_assets/database/data/iceland/iceland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_insurance_general.xlsx
@@ -588,100 +588,103 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.127</v>
+        <v>0.0848</v>
+      </c>
+      <c r="E2">
+        <v>0.0645</v>
       </c>
       <c r="G2">
-        <v>0.1955353451839603</v>
+        <v>0.4171011470281543</v>
       </c>
       <c r="H2">
-        <v>0.1955353451839603</v>
+        <v>0.4171011470281543</v>
       </c>
       <c r="I2">
-        <v>0.3513848697809012</v>
+        <v>0.1350364963503649</v>
       </c>
       <c r="J2">
-        <v>0.3288962381149235</v>
+        <v>0.1213758275335257</v>
       </c>
       <c r="K2">
-        <v>79.59999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="L2">
-        <v>0.3290615957007028</v>
+        <v>0.1209593326381647</v>
       </c>
       <c r="M2">
-        <v>27.91</v>
+        <v>59</v>
       </c>
       <c r="N2">
-        <v>0.07545282508786158</v>
+        <v>0.2142338416848221</v>
       </c>
       <c r="O2">
-        <v>0.3506281407035176</v>
+        <v>2.543103448275862</v>
       </c>
       <c r="P2">
-        <v>20.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q2">
-        <v>0.05515004055150041</v>
+        <v>0.09549745824255629</v>
       </c>
       <c r="R2">
-        <v>0.2562814070351759</v>
+        <v>1.133620689655172</v>
       </c>
       <c r="S2">
-        <v>7.509999999999998</v>
+        <v>32.7</v>
       </c>
       <c r="T2">
-        <v>0.2690791830884987</v>
+        <v>0.5542372881355933</v>
       </c>
       <c r="U2">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="V2">
-        <v>0.03190051365233847</v>
+        <v>0.04320987654320988</v>
       </c>
       <c r="W2">
-        <v>0.5993975903614457</v>
+        <v>0.1202695697252462</v>
       </c>
       <c r="X2">
-        <v>0.05060450917639508</v>
+        <v>0.085162043359804</v>
       </c>
       <c r="Y2">
-        <v>0.5487930811850505</v>
+        <v>0.03510752636544223</v>
       </c>
       <c r="Z2">
-        <v>1.941412520064205</v>
+        <v>1.002613695765813</v>
       </c>
       <c r="AA2">
-        <v>0.6385232744783306</v>
+        <v>0.1216930670200221</v>
       </c>
       <c r="AB2">
-        <v>0.04990263419319146</v>
+        <v>0.08387619678736756</v>
       </c>
       <c r="AC2">
-        <v>0.5886206402851392</v>
+        <v>0.03781687023265458</v>
       </c>
       <c r="AD2">
-        <v>10.2</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10.2</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AG2">
-        <v>-1.600000000000001</v>
+        <v>-2.52</v>
       </c>
       <c r="AH2">
-        <v>0.02683504340962905</v>
+        <v>0.0329377062995997</v>
       </c>
       <c r="AI2">
-        <v>0.05022156573116691</v>
+        <v>0.06360184431787362</v>
       </c>
       <c r="AJ2">
-        <v>-0.004344284550638071</v>
+        <v>-0.009234828496042215</v>
       </c>
       <c r="AK2">
-        <v>-0.008363826450601157</v>
+        <v>-0.01858681221419088</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.1192982456140351</v>
+        <v>0.3553030303030303</v>
       </c>
       <c r="AP2">
-        <v>-0.01871345029239768</v>
+        <v>-0.09545454545454544</v>
       </c>
     </row>
     <row r="3">
@@ -713,100 +716,103 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.127</v>
+        <v>0.0848</v>
+      </c>
+      <c r="E3">
+        <v>0.0645</v>
       </c>
       <c r="G3">
-        <v>0.1955353451839603</v>
+        <v>0.4171011470281543</v>
       </c>
       <c r="H3">
-        <v>0.1955353451839603</v>
+        <v>0.4171011470281543</v>
       </c>
       <c r="I3">
-        <v>0.3513848697809012</v>
+        <v>0.1350364963503649</v>
       </c>
       <c r="J3">
-        <v>0.3288962381149235</v>
+        <v>0.1213758275335257</v>
       </c>
       <c r="K3">
-        <v>79.59999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="L3">
-        <v>0.3290615957007028</v>
+        <v>0.1209593326381647</v>
       </c>
       <c r="M3">
-        <v>27.91</v>
+        <v>59</v>
       </c>
       <c r="N3">
-        <v>0.07545282508786158</v>
+        <v>0.2142338416848221</v>
       </c>
       <c r="O3">
-        <v>0.3506281407035176</v>
+        <v>2.543103448275862</v>
       </c>
       <c r="P3">
-        <v>20.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q3">
-        <v>0.05515004055150041</v>
+        <v>0.09549745824255629</v>
       </c>
       <c r="R3">
-        <v>0.2562814070351759</v>
+        <v>1.133620689655172</v>
       </c>
       <c r="S3">
-        <v>7.509999999999998</v>
+        <v>32.7</v>
       </c>
       <c r="T3">
-        <v>0.2690791830884987</v>
+        <v>0.5542372881355933</v>
       </c>
       <c r="U3">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="V3">
-        <v>0.03190051365233847</v>
+        <v>0.04320987654320988</v>
       </c>
       <c r="W3">
-        <v>0.5993975903614457</v>
+        <v>0.1202695697252462</v>
       </c>
       <c r="X3">
-        <v>0.05060450917639508</v>
+        <v>0.085162043359804</v>
       </c>
       <c r="Y3">
-        <v>0.5487930811850505</v>
+        <v>0.03510752636544223</v>
       </c>
       <c r="Z3">
-        <v>1.941412520064205</v>
+        <v>1.002613695765813</v>
       </c>
       <c r="AA3">
-        <v>0.6385232744783306</v>
+        <v>0.1216930670200221</v>
       </c>
       <c r="AB3">
-        <v>0.04990263419319146</v>
+        <v>0.08387619678736756</v>
       </c>
       <c r="AC3">
-        <v>0.5886206402851392</v>
+        <v>0.03781687023265458</v>
       </c>
       <c r="AD3">
-        <v>10.2</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10.2</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AG3">
-        <v>-1.600000000000001</v>
+        <v>-2.52</v>
       </c>
       <c r="AH3">
-        <v>0.02683504340962905</v>
+        <v>0.0329377062995997</v>
       </c>
       <c r="AI3">
-        <v>0.05022156573116691</v>
+        <v>0.06360184431787362</v>
       </c>
       <c r="AJ3">
-        <v>-0.004344284550638071</v>
+        <v>-0.009234828496042215</v>
       </c>
       <c r="AK3">
-        <v>-0.008363826450601157</v>
+        <v>-0.01858681221419088</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.1192982456140351</v>
+        <v>0.3553030303030303</v>
       </c>
       <c r="AP3">
-        <v>-0.01871345029239768</v>
+        <v>-0.09545454545454544</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/iceland/iceland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_insurance_general.xlsx
@@ -588,103 +588,103 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0848</v>
+        <v>0.119</v>
       </c>
       <c r="E2">
-        <v>0.0645</v>
+        <v>0.417</v>
       </c>
       <c r="G2">
-        <v>0.4171011470281543</v>
+        <v>0.09864687909209953</v>
       </c>
       <c r="H2">
-        <v>0.4171011470281543</v>
+        <v>0.09864687909209953</v>
       </c>
       <c r="I2">
-        <v>0.1350364963503649</v>
+        <v>0.1396769969445657</v>
       </c>
       <c r="J2">
-        <v>0.1213758275335257</v>
+        <v>0.1197900586600803</v>
       </c>
       <c r="K2">
-        <v>23.2</v>
+        <v>28.1</v>
       </c>
       <c r="L2">
-        <v>0.1209593326381647</v>
+        <v>0.1226538629419468</v>
       </c>
       <c r="M2">
-        <v>59</v>
+        <v>18.38</v>
       </c>
       <c r="N2">
-        <v>0.2142338416848221</v>
+        <v>0.05394775462283535</v>
       </c>
       <c r="O2">
-        <v>2.543103448275862</v>
+        <v>0.6540925266903915</v>
       </c>
       <c r="P2">
-        <v>26.3</v>
+        <v>13.8</v>
       </c>
       <c r="Q2">
-        <v>0.09549745824255629</v>
+        <v>0.04050484297035516</v>
       </c>
       <c r="R2">
-        <v>1.133620689655172</v>
+        <v>0.4911032028469751</v>
       </c>
       <c r="S2">
-        <v>32.7</v>
+        <v>4.580000000000002</v>
       </c>
       <c r="T2">
-        <v>0.5542372881355933</v>
+        <v>0.249183895538629</v>
       </c>
       <c r="U2">
-        <v>11.9</v>
+        <v>25.5</v>
       </c>
       <c r="V2">
-        <v>0.04320987654320988</v>
+        <v>0.07484590548869974</v>
       </c>
       <c r="W2">
-        <v>0.1202695697252462</v>
+        <v>0.2034757422157857</v>
       </c>
       <c r="X2">
-        <v>0.085162043359804</v>
+        <v>0.07597389647116216</v>
       </c>
       <c r="Y2">
-        <v>0.03510752636544223</v>
+        <v>0.1275018457446235</v>
       </c>
       <c r="Z2">
-        <v>1.002613695765813</v>
+        <v>1.689777253282195</v>
       </c>
       <c r="AA2">
-        <v>0.1216930670200221</v>
+        <v>0.2024185162931435</v>
       </c>
       <c r="AB2">
-        <v>0.08387619678736756</v>
+        <v>0.07506340172554649</v>
       </c>
       <c r="AC2">
-        <v>0.03781687023265458</v>
+        <v>0.127355114567597</v>
       </c>
       <c r="AD2">
-        <v>9.380000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9.380000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG2">
-        <v>-2.52</v>
+        <v>-15.7</v>
       </c>
       <c r="AH2">
-        <v>0.0329377062995997</v>
+        <v>0.02796005706134094</v>
       </c>
       <c r="AI2">
-        <v>0.06360184431787362</v>
+        <v>0.05990220048899755</v>
       </c>
       <c r="AJ2">
-        <v>-0.009234828496042215</v>
+        <v>-0.04830769230769231</v>
       </c>
       <c r="AK2">
-        <v>-0.01858681221419088</v>
+        <v>-0.113685734974656</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.3553030303030303</v>
+        <v>0.3015384615384615</v>
       </c>
       <c r="AP2">
-        <v>-0.09545454545454544</v>
+        <v>-0.4830769230769231</v>
       </c>
     </row>
     <row r="3">
@@ -716,103 +716,103 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0848</v>
+        <v>0.119</v>
       </c>
       <c r="E3">
-        <v>0.0645</v>
+        <v>0.417</v>
       </c>
       <c r="G3">
-        <v>0.4171011470281543</v>
+        <v>0.09864687909209953</v>
       </c>
       <c r="H3">
-        <v>0.4171011470281543</v>
+        <v>0.09864687909209953</v>
       </c>
       <c r="I3">
-        <v>0.1350364963503649</v>
+        <v>0.1396769969445657</v>
       </c>
       <c r="J3">
-        <v>0.1213758275335257</v>
+        <v>0.1197900586600803</v>
       </c>
       <c r="K3">
-        <v>23.2</v>
+        <v>28.1</v>
       </c>
       <c r="L3">
-        <v>0.1209593326381647</v>
+        <v>0.1226538629419468</v>
       </c>
       <c r="M3">
-        <v>59</v>
+        <v>18.38</v>
       </c>
       <c r="N3">
-        <v>0.2142338416848221</v>
+        <v>0.05394775462283535</v>
       </c>
       <c r="O3">
-        <v>2.543103448275862</v>
+        <v>0.6540925266903915</v>
       </c>
       <c r="P3">
-        <v>26.3</v>
+        <v>13.8</v>
       </c>
       <c r="Q3">
-        <v>0.09549745824255629</v>
+        <v>0.04050484297035516</v>
       </c>
       <c r="R3">
-        <v>1.133620689655172</v>
+        <v>0.4911032028469751</v>
       </c>
       <c r="S3">
-        <v>32.7</v>
+        <v>4.580000000000002</v>
       </c>
       <c r="T3">
-        <v>0.5542372881355933</v>
+        <v>0.249183895538629</v>
       </c>
       <c r="U3">
-        <v>11.9</v>
+        <v>25.5</v>
       </c>
       <c r="V3">
-        <v>0.04320987654320988</v>
+        <v>0.07484590548869974</v>
       </c>
       <c r="W3">
-        <v>0.1202695697252462</v>
+        <v>0.2034757422157857</v>
       </c>
       <c r="X3">
-        <v>0.085162043359804</v>
+        <v>0.07597389647116216</v>
       </c>
       <c r="Y3">
-        <v>0.03510752636544223</v>
+        <v>0.1275018457446235</v>
       </c>
       <c r="Z3">
-        <v>1.002613695765813</v>
+        <v>1.689777253282195</v>
       </c>
       <c r="AA3">
-        <v>0.1216930670200221</v>
+        <v>0.2024185162931435</v>
       </c>
       <c r="AB3">
-        <v>0.08387619678736756</v>
+        <v>0.07506340172554649</v>
       </c>
       <c r="AC3">
-        <v>0.03781687023265458</v>
+        <v>0.127355114567597</v>
       </c>
       <c r="AD3">
-        <v>9.380000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9.380000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3">
-        <v>-2.52</v>
+        <v>-15.7</v>
       </c>
       <c r="AH3">
-        <v>0.0329377062995997</v>
+        <v>0.02796005706134094</v>
       </c>
       <c r="AI3">
-        <v>0.06360184431787362</v>
+        <v>0.05990220048899755</v>
       </c>
       <c r="AJ3">
-        <v>-0.009234828496042215</v>
+        <v>-0.04830769230769231</v>
       </c>
       <c r="AK3">
-        <v>-0.01858681221419088</v>
+        <v>-0.113685734974656</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.3553030303030303</v>
+        <v>0.3015384615384615</v>
       </c>
       <c r="AP3">
-        <v>-0.09545454545454544</v>
+        <v>-0.4830769230769231</v>
       </c>
     </row>
   </sheetData>
